--- a/build/filters/questions-2026-08-06/Questions-for-Branko-Cicovic_Filters-and-Schedule_2026-08-06.xlsx
+++ b/build/filters/questions-2026-08-06/Questions-for-Branko-Cicovic_Filters-and-Schedule_2026-08-06.xlsx
@@ -738,7 +738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -759,7 +759,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>FOUR ITEMS, AND AN APOLOGY WITH THE FIRST. Question 1 was written on 22 July and we never actually sent it to you. Two tests have been sitting parked ever since waiting for an answer you were never asked for. That delay is ours, not yours. Nothing here is a complaint, and one of these is honestly our own fault for not sending it sooner. It covers TWO of your projects, so every question says which one it belongs to - Filters or Schedule - and the tabs are split the same way. It is gathered into one place so you can go through it in a single sitting rather than getting a trickle of separate messages.</t>
+          <t>EIGHT ITEMS, AND AN APOLOGY WITH THE FIRST. Question 1 was written on 22 July and we never actually sent it to you. Two tests have been sitting parked ever since waiting for an answer you were never asked for. That delay is ours, not yours. QUESTIONS 5 AND 6 ARE THE TWO THAT MATTER MOST: each one decides whether a test of ours is right or wrong, and both come out of the changes made to your own description this morning. Nothing here is a complaint, and one of these is honestly our own fault for not sending it sooner. It covers TWO of your projects, so every question says which one it belongs to - Filters or Schedule - and the tabs are split the same way. It is gathered into one place so you can go through it in a single sitting rather than getting a trickle of separate messages.</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>FOUR SCHEDULE ITEMS - THREE TESTS ARE ON HOLD</t>
+          <t>EIGHT SCHEDULE ITEMS - FIVE OF OUR TESTS ARE WAITING ON YOUR ANSWERS</t>
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
@@ -933,6 +933,130 @@
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr"/>
+    </row>
+    <row r="10" ht="300" customHeight="1">
+      <c r="A10" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Schedule (the technician scheduling calendar) - the search box in the toolbar above the calendar grid (not the one in the job list down the left) (the story about the calendar layout, SV-8686, under epic SV-8685)</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>THIS ONE DECIDES WHETHER ONE OF OUR TESTS IS RIGHT OR WRONG, so it is worth a minute.
+Your written description used to say that when someone searches, the jobs that do not match go FADED BUT STAY ON SCREEN, so you keep sight of the whole week. That sentence was taken out of the description THIS MORNING, after your team decided the description was wrong and that the drawing shows only the matching jobs. The description now says only WHAT the search looks through - customer name, work order number, unit number, technician name and line name. It no longer says anything at all about what happens to the jobs that do NOT match.
+Our test still says the non-matching jobs go faded, because that is what was written down when we wrote it. We are not going to quietly change it to match what the software does today, because that would tell us what was built rather than what you wanted.
+One more thing in the same place: the developer ticket that describes the calendar layout STILL says the non-matching jobs should fade - in two places, in its requirements and again in its acceptance criteria. So your description and that ticket now disagree with each other. If your answer is A, somebody should tidy that ticket up. We have not touched it, because it is not ours.</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>When someone searches, what should happen to the jobs that do not match?</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>A) They should disappear from the calendar - only the matching jobs are shown. (This is what your team said the drawing shows.)
+B) They should stay on screen but faded, and the matching ones stand out.
+C) Something else - please describe it.</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr"/>
+    </row>
+    <row r="11" ht="300" customHeight="1">
+      <c r="A11" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Schedule (the technician scheduling calendar) - the pop-up window that opens when you click a scheduled job (the story about that window, SV-8695, under epic SV-8685)</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>THIS ONE DECIDES WHETHER A TEST PASSES OR FAILS, which is exactly why we are asking instead of choosing.
+Earlier today, on the report about that window, you told us the little ESTIMATE BADGE should not be clickable, and that the time is changed in the fields higher up the window instead. That makes sense to us.
+What we cannot tell is how far your answer reaches. Your written description STILL says the window should let someone type a new estimate straight into it, and the developer ticket for that window still says the same. Both of those are live today. So your sentence might mean the estimate cannot be changed anywhere in that window, or it might mean only that the small badge on the job line should not be clickable.
+We have one test that says the estimate CAN be typed into. If you mean the first, that test is wrong and we will correct it. If you mean the second, the test is right and the software has something to fix. We are deliberately not settling it by looking at what the software does today.</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>In that pop-up window, should someone be able to change the ESTIMATED HOURS by typing into them?</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>A) NO - the estimate cannot be changed in that window at all; only the start and end times can be changed, in the fields above.
+B) YES - the estimate itself can still be typed into; only the little badge on the job line should not be clickable.
+C) Something else - please describe it.</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr"/>
+    </row>
+    <row r="12" ht="300" customHeight="1">
+      <c r="A12" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Schedule (the technician scheduling calendar) - the list of jobs INSIDE that same pop-up window (the story about that window, SV-8695, under epic SV-8685)</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>This one is small, and it is only two of your own documents disagreeing with each other.
+Your written description was changed this morning so that each job line in that pop-up shows an estimate figure and a status label. In your own words earlier today, the lines should show the estimate and the status badge and there should not be any totals. Our test already expects exactly that - the hours and a status label, and no money anywhere in the window - so nothing of ours is stuck.
+But the developer ticket for that window still says each line shows a labour TOTAL, and it has said so since before your change. You edited that same ticket three days ago and the word is still sitting in it. So your description and that ticket now say different things, and only you can say which one is the one to keep.
+While you are in that ticket: it also still says the estimate can be typed in, which is the question just above this one. Both would be tidied up in the same visit.</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>On each job line in that pop-up, should there be a money total, or only the hours and a status label?</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>A) ONLY the hours and a status label - no money anywhere. Your description is right and the developer ticket needs tidying up.
+B) A MONEY TOTAL should be shown there - the developer ticket is right and your description needs correcting. (Then our test is wrong and we will change it.)
+C) Something else - please describe it.</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13" ht="300" customHeight="1">
+      <c r="A13" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Schedule (the technician scheduling calendar) - how much of the day the timeline shows when the day view opens (under epic SV-8685)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Nothing is stuck on this one and no test of ours is wrong today. We are asking so that we are not quietly relying on a note that disagrees with your own description.
+Your description says the day view keeps the WHOLE 24 HOURS there and scrollable, and simply scrolls itself so the start of the working day is on the left.
+A note on one of the design-review reports asks for something different: that the timeline show ONLY THE WORKING HOURS plus a small amount after them, with anything outside that reached by scrolling. That note says it is being tracked as a later improvement rather than for this release, which is why we have left our test alone.
+If the narrower version is meant for this release, your description needs changing first and then we will change the test to match it.</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>For THIS release, which is right?</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>A) Keep the full 24 hours, as your description says today - the narrower version is for later.
+B) Change it now to show only the working hours plus a small amount after them.
+C) Something else - please describe it.</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1203,7 +1327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1569,110 +1693,299 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Tab 3</t>
+          <t>Tab 2</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>1-6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Schedule - six behaviours only the engineering plan describes: pre-existing shifts and events · a multi-day job on the Dashboard · an appointment set while creating a job · jobs from another branch · the priority on a job · a limit on how long a spread can be</t>
+          <t>Schedule - what should happen to the calendar blocks that do NOT match the toolbar search?</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>CARRIED FORWARD VERBATIM from the 2026-08-05 sheet's engineering-only tab. All six were re-checked against spec v25 today and all six are STILL absent from it.</t>
+          <t>NEW, from the Schedule spec v23 -&gt; v25 diff: Q1 of build/schedule/spec-v25-2026-08-06/QUESTIONS-FOR-BRANKO.md. Confluence **v24** DELETED the fade/highlight requirement; the PRD is now SILENT on what happens instead.</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>No case is held on these six. They are candidate coverage rather than blocked coverage - Rule 30 forbids turning an engineering plan into a product requirement without the PO.</t>
+          <t>ONE case, and his answer decides what it should ASSERT - SCH-TOOL-03 (C30041). It is NOT on HOLD today; it carries AUTOMATION: READY - EXPECT FAIL (SV-8874), and a HOLD is PROPOSED pending this answer (spec-v25-2026-08-06/PROPOSED-CHANGES.md §2).</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>(no held cases)</t>
+          <t>C30041 https://shopview.testrail.io/index.php?/cases/view/30041</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>VERIFIED LIVE 2026-08-06 against Schedule spec v25, searching the whole body: pre-existing shifts/migration = 0 matches · dashboard = 0 · appointment = 0 · another branch / cross-location = 0 · spread length limit (8 weeks / 120 shifts / maximum span) = 0. Only "priority" appears, and only as a bare field name with no behaviour attached. So none of the six was answered by the v23 -&gt; v25 edits.</t>
+          <t>VERIFIED LIVE 2026-08-06, read-only. Schedule Confluence page 713031682 at VERSION 25 (2026-08-06T09:13:51Z, HTTP 200): §6 now reads only "Search - Filters grid blocks by matching against customer name, WO number, unit number, technician name, and line name." Searched the whole v25 body: "non-matching" = 0 hits, "de-emphas" = 0, "dim" = 0; the single "faded" hit is the series "continues" label and is unrelated. SO THE PRD IS SILENT, NOT REVERSED. JIRA READ LIVE: SV-8686 (Story, TESTING QA, parent SV-8685) STILL CARRIES IT TWICE - Requirements verbatim "Non-matching blocks fade; matching blocks highlight. - (PRD: §6)" and Acceptance Criteria verbatim "...then matching blocks highlight and non-matching blocks fade." SV-8874 (Story Defect, parent SV-8686) is OBSOLETE/Done, resolved 2026-08-06T03:32:42-0500 by Milos Vasic, whose comment reads "All good on this one updated the PRD , i will close this ticket as absolute", 81 seconds before v24. TESTRAIL READ LIVE: C30041's title is "Toolbar search highlights matching blocks and fades non-matching ones" and expected item 1 is "Blocks that match the search are highlighted; blocks that do not match fade." - so the deleted requirement is in the title AND the body.</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>Each answer either creates authorable coverage or closes the item as out of scope. Nothing here is urgent, which is why it is the last tab - but leaving them off would make six deliberate omissions indistinguishable from six misses (Rule 46).</t>
+          <t>A -&gt; the fade assertion is REMOVED and the case asserts non-matching blocks are gone; marker becomes READY. B -&gt; the build has a real defect and SV-8874 was closed wrongly. EITHER WAY THE MARKER IS ALREADY WRONG, because it names SV-8874 as an open expect-fail and SV-8874 is closed. Rule 57 is why this is asked and not read off the build: the PRD's SILENCE licenses REMOVING our assertion, it does not license asserting the opposite. Stefan Vukovic's "per design we show only shifts/events that are matching the search" (2026-08-06T03:15:35-0500) is an ENGINEER's statement about a design we do not hold, so it is not a PO ruling (Rule 33). SV-8686 is the OWNER's to correct - Rule 38, not ours to edit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Tab 2</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Schedule - can the estimated hours still be typed into inside the shift window?</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>NEW, Q2 of the same file, and THE SHARPEST ROW ON THE SHEET: it is the difference between a case that passes and a case that fails on the same build. Branko's own ruling created the ambiguity 17 minutes after he published v25.</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>ONE case - SCH-MODAL-05 (C30012). Currently AUTOMATION: READY, i.e. we expect it to PASS, while the PO has closed a report saying the build does not allow the edit. A HOLD is PROPOSED, not applied (PROPOSED-CHANGES.md §5).</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>C30012 https://shopview.testrail.io/index.php?/cases/view/30012</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>VERIFIED LIVE 2026-08-06, read-only. v25 §4.9 STILL READS "Estimated hours with inline edit." - the spec line was NOT changed by v24 or v25. SV-8695 (Story, Ready for QA) Requirements verbatim: "...scope summary with scheduled line(s) and labor/total, estimated hours with inline edit..." - SO TWO WRITTEN SOURCES STILL REQUIRE IT. Against that, SV-8829 (Story Defect, OBSOLETE/Done, parent SV-8695) carries Branko Cicovic's ONLY comment, at 2026-08-06T04:31:05-0500 = 09:31:05Z, SEVENTEEN MINUTES AFTER v25 was published at 09:13:51Z, verbatim: "Estimated badge should not be clickable, you can change time only in the input fields above. I updated PRD, for work order lines we just show estimate and status badge, there shouldn't be totals. Please always check the design as it is single source of truth." THE AMBIGUITY IS SCOPE: SV-8829's own steps distinguish the LINE ROW's badge ("only 1h and an Authorized badge") from the MODAL-level "estimated hours with inline edit", and his sentence names "the Estimated badge". TestRail read live: C30012 = "Estimated hours can be edited inline in the modal", refs SV-8695 (§4.9 (Estimated hours with inline edit)), marker READY.</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>A -&gt; the case is WRONG, is rewritten, and both the spec line and SV-8695 are stale. B -&gt; the case is RIGHT and SV-8829 was closed wrongly, so a defect is owed. Rule 58 is the whole reason this is a question: an ambiguous source is NEVER resolved by looking at what the build does - and flipping the case off two written sources onto one ambiguous sentence would be the Filters mistake in reverse.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>HONESTY AND METHOD NOTES</t>
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Tab 2</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Schedule - his own story still says the shift window's job lines show a labour TOTAL, while his own spec now says a labour/status figure</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>NEW, and it is the row the QA lead asked for explicitly: a small inconsistency between two of HIS OWN documents that he owes. It also carries the second half of item 6's tidy-up.</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>ONE case, and it does NOT change under answer A - SCH-MODAL-04 (C30011). Marker AUTOMATION: READY. PROPOSED-CHANGES.md §1 proposes a provenance/divergence edit only, no assertion change.</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>C30011 https://shopview.testrail.io/index.php?/cases/view/30011</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>VERIFIED LIVE 2026-08-06, read-only. v25 §4.9 verbatim: "Scope summary and the scheduled line(s) with labor/status figures." SV-8695 Requirements verbatim, STILL: "...scope summary with scheduled line(s) and labor/total..." - and per the v25 diff pass that phrase is present both BEFORE AND AFTER Branko's own description edit of 2026-08-03T08:54:30Z, so the PO edited this story three days ago and left `total` standing, then changed the PRD on 2026-08-06. THREE SOURCES AGREE AND ONE LAGS: his 22 July no-money-on-the-Schedule ruling, PRD v25 (`labor/status`), and his SV-8829 comment ("we just show estimate and status badge, there shouldn't be totals") all say no totals; SV-8695 alone still says `total`. TestRail read live: C30011 = "The modal lists the scheduled line(s) with no money fields", expected items 2-3 verbatim "...each showing its line number, title, hours, and a status pill only. 3. No labor figures and no total dollar amount appear anywhere in the modal." - so under Rules 32/33 the case ALREADY follows the three, which is why nothing is blocked on this row.</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>A (expected) -&gt; nothing changes in the case; SV-8695 is corrected BY ITS OWNER (Rule 38). B -&gt; C30011 is wrong and item 3 of its expected result must be rewritten, and the PRD needs correcting too. NOTE FOR THE QA LEAD ON WHAT WAS DELIBERATELY *NOT* ASKED: the source file's Q2b asked what the WORD "labor" means in "labor/status figures" - hours or money. That was LEFT OFF, because his SV-8829 comment already answers it in his own words and, on the source file's own admission, NEITHER answer changes the case's substance. Asking it would have re-asked a settled point for zero test consequence. Its one live consequence - that two of his documents now disagree - is THIS row. Our own text using "labor" for both hours and money in C30011 is an internal wording repair, not a product question.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>WHY ONE FILE AND NOT TWO (Standing Rule 55). build/branko-questions-2026-08-05/ holds a 13-item Branko sheet that is READY TO SEND and WAS NEVER SENT (register row C4). Producing a second sheet without absorbing it would leave the QA lead holding two unsent sheets for the same person - the exact 'drip of separate asks' Rule 55 exists to prevent. So this workbook CARRIES FORWARD all 13 of its items and adds 4 new ones = 17. ⚠️ ACTION NEEDED FROM THE QA LEAD: the 2026-08-05 workbook should be marked SUPERSEDED so an old one cannot go out by mistake. It was NOT edited by this pass, because this task was scoped to write only inside build/filters/questions-2026-08-06/ and build/report-suite/questions-2026-08-06/.</t>
+          <t>Tab 2</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Schedule - for this release, does the day view keep the full 24 hours or only the working hours plus a buffer?</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>NEW, Q3 of the same file. Asked so we are not silently relying on a change-request note that contradicts the live spec - not because any case is wrong today.</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>ONE case, and NO change is proposed to it - SCH-DAY-01 (C30001). It is correct against v25 as written and already covers the full start-time hierarchy.</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>C30001 https://shopview.testrail.io/index.php?/cases/view/30001</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>VERIFIED LIVE 2026-08-06, read-only. v25 §4.8 verbatim: "The full 24-hour timeline remains intact and scrollable.", and §3.2: "Day view. A 24-hour timeline per technician row with time-positioned blocks." Against that, SV-8915 (Bug, OBSOLETE/Done, parent SV-8685, reporter Sasha Grosman) carries under "Related change requests", verbatim: "Schedule width should render only business hours plus a small trailing buffer rather than the full 24 hours; after-hours scheduling is an edge case reachable by scrolling. Tracked separately on the enhancements list for the Schedule design." TestRail read live: C30001 = "Day view auto-scrolls to the working-day start; manual scrolling stands", refs SV-8694 (§4.8 (Auto-scroll to business hours)), marker AUTOMATION: READY - EXPECT FAIL (SV-8837) - and SV-8837 is live-confirmed STILL OPEN (Story Defect, Ready for QA, parent SV-8694), so that marker is correct and untouched by this question.</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>A (recommended, and what the spec says today) -&gt; nothing changes; the item closes in the decisions register as out of V1. B -&gt; §4.8 becomes wrong and needs a spec edit BEFORE any case change - the spec is corrected first, never the case. SV-8915 is ALSO the design-authority ticket, which is why its other half sits on Schedule item 4 of this sheet rather than here.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>HOW DRIFT WAS PREVENTED: every carried-forward reader-facing row is IMPORTED from the 2026-08-05 generator's own TAB1/TAB2/TAB3 lists at build time, not retyped. So the 13 carried items are byte-identical to the rows that sheet carried - the same technique the 2026-08-04 Chris consolidation used. Only the 4 new items and the tab notes are new text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>SV-8876 IS DELIBERATELY NOT ON THIS SHEET, AND THE BRIEF FOR THIS TASK WAS WRONG ABOUT IT. The brief listed it as "Ahtasham's clarification question, still his to answer", and CLAUDE.md's Filters section says "Branko owes SV-8876". READ LIVE FROM JIRA 2026-08-06: SV-8876 is a Task, status DONE, resolution Done, resolved 2026-08-05T08:38:16-0500, parent SV-8785, reporter Ahtasham Amjad. He CLOSED IT HIMSELF, with one comment, verbatim: "closing this as it was a gap with test case , I've updated the test case here &gt;&gt;https://shopview.testrail.io/index.php?/cases/view/29557 And created a story defect &gt;&gt; as the build is not behaving as per PRD". Putting it in front of Branko would have re-asked a closed question - the exact embarrassment this project has already had once. THE HALF THAT IS GENUINELY STILL HIS is the narrower one and IS on the sheet, as Filters item 5: did he want the buttons on one row, in which case the developer job should be cancelled? SEPARATE POINT FOR THE QA LEAD, NOT FOR BRANKO: that comment says Ahtasham EDITED OUR CASE C29557. Under Rule 38 we do not touch his cases and he should not be editing ours; this is reported, not acted on.</t>
+          <t>Tab 3</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>1-6</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Schedule - six behaviours only the engineering plan describes: pre-existing shifts and events · a multi-day job on the Dashboard · an appointment set while creating a job · jobs from another branch · the priority on a job · a limit on how long a spread can be</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>CARRIED FORWARD VERBATIM from the 2026-08-05 sheet's engineering-only tab. All six were re-checked against spec v25 today and all six are STILL absent from it.</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>No case is held on these six. They are candidate coverage rather than blocked coverage - Rule 30 forbids turning an engineering plan into a product requirement without the PO.</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>(no held cases)</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>VERIFIED LIVE 2026-08-06 against Schedule spec v25, searching the whole body: pre-existing shifts/migration = 0 matches · dashboard = 0 · appointment = 0 · another branch / cross-location = 0 · spread length limit (8 weeks / 120 shifts / maximum span) = 0. Only "priority" appears, and only as a bare field name with no behaviour attached. So none of the six was answered by the v23 -&gt; v25 edits.</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Each answer either creates authorable coverage or closes the item as out of scope. Nothing here is urgent, which is why it is the last tab - but leaving them off would make six deliberate omissions indistinguishable from six misses (Rule 46).</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>THE FILTERS SPEC MOVED TO VERSION 19 THIS MORNING AND NO QUESTION WAS MANUFACTURED FROM IT. Page 572030978, version 19, 2026-08-06T11:48:47Z. Its visible change on the filter bar is S1-R3, verbatim: "Each chip displays a leading type-icon identifying the filter, the filter name, and a chevron icon indicating it opens a dropdown". THAT IS CLEAR ENOUGH TO TEST - a tester can check that each chip carries a leading icon plus a chevron, and which specific icon belongs to which chip comes from the design node the spec links. So NO ROW WAS ADDED for it (Rule 55 says ask what is unclear; it does not say invent an ask). What v19 did NOT do is resolve anything on this sheet: S9-R2 and S9-R3 are unchanged, and the S12-R2 cross-reference is still wrong. ⚠️ OWED: a proper v18 -&gt; v19 diff. This pass checked the points the sheet depends on, not the whole document, and does not claim to have diffed it.</t>
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>HONESTY AND METHOD NOTES</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>THE SCHEDULE SPEC HAS MOVED 23 -&gt; 25 AND WE HAVE NOT DIFFED IT. Page 713031682 is at VERSION 25 (2026-08-06T09:13:51Z) while CLAUDE.md and build/OUTSTANDING-ITEMS-REGISTER.md both name version 23. TWO VERSIONS OF PRODUCT CHANGE ARE UNINGESTED on an active project. What was checked live today is only what this sheet rests on: both shop-closure sentences survive, both click-menu wordings survive, and all six engineering-only topics are still absent. Nothing else about v24 or v25 is known. This is a genuine outstanding item and is reported rather than glossed (Rules 31 and 59).</t>
+          <t>ADDENDUM 2026-08-06 - FOUR SCHEDULE ITEMS ADDED, TAKING THE SHEET FROM 17 TO 21. They come from build/schedule/spec-v25-2026-08-06/QUESTIONS-FOR-BRANKO.md, the Schedule spec v23 -&gt; v25 diff. They are APPENDED as Schedule items 5-8 rather than re-ordered into the tab, so the established structure and the carried-forward wording are untouched (Rule 16); the tab note names items 5 and 6 as the decisive ones so their importance is still visible on the reader tab. TWO OF THEM EACH DECIDE A VERDICT: item 5 decides what C30041 should assert, item 6 decides whether C30012 passes or fails. Nothing was applied to TestRail - no case was edited, and the HOLDs those two items imply are PROPOSED in PROPOSED-CHANGES.md, not written.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>WORDING RULES APPLIED (Standing Rules 7 and 55): every reader-facing question row names the PROJECT (Filters or Schedule) and the SCREEN, because Branko owns THREE projects - Filters, Schedule and Global Search - so a row read on its own, days later, on a phone must still be unambiguous. Story and epic keys appear in plain form only where they orient him. No case IDs, no requirement anchors, no technical terms and not the word VIU appear anywhere he reads. Each question is a plain A/B/C with a blank for the answer, and each carries a one-line reason so the consequence is visible.</t>
+          <t>ONE OF THE FOUR SOURCE QUESTIONS WAS DELIBERATELY LEFT OFF, AND THIS IS THE REASON (Rule 55: ask what is unclear; it does not say invent an ask). The source file's Q2b asked what the word "labor" means in v25's new phrase "labor/status figures" - the number of HOURS or a MONEY amount. It is NOT asked, on two grounds, both checked rather than assumed. FIRST, HE HAS ALREADY ANSWERED IT IN HIS OWN WORDS: SV-8829, 2026-08-06T04:31:05-0500, verbatim "for work order lines we just show estimate and status badge, there shouldn't be totals" - which, with his 22 July no-money-on-the-Schedule ruling, says plainly that no money appears. SECOND, THE SOURCE FILE ITSELF RECORDS THAT NEITHER ANSWER CHANGES THE CASE: "Neither answer changes the case's substance; A confirms it as written." So it would have cost a PO round trip for zero test consequence - and re-asking something a source has already settled is the exact embarrassment this project has had once already. ITS ONE GENUINELY LIVE CONSEQUENCE IS ON THE SHEET as Schedule item 7: that his STORY and his SPEC now disagree (`labor/total` vs `labor/status`), which is a fork with a real answer and a named owner. The residual ambiguity is in OUR OWN text - C30011 uses "labor" for both hours and money in one expected result - and that is an internal wording repair, not a question for a product owner.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>SOURCE-CURRENCY (Standing Rules 31 and 59), fetched LIVE and re-read immediately before writing, 2026-08-06: Filters spec page 572030978 = VERSION 19, HTTP 200 (in-body field still reads "Version: 1.6" - the Rule-31(a) trap; the CONFLUENCE number is the one used). Schedule spec page 713031682 = VERSION 25, HTTP 200, and STALE against our records at 23. Jira read live for SV-8876, SV-8825, SV-8915, SV-8916, SV-8917. TestRail read live for all 114 Filters cases. Schedule cases were NOT re-pulled this pass - the three held C-ids above are taken from the project's committed records and are cited as such. Designs = PARTIAL, and which artefact is canonical is Schedule item 4 on this very sheet.</t>
+          <t>THE DESIGN-AUTHORITY QUESTION WAS DELIBERATELY *NOT* ADDED AS A NEW ROW, ON THE QA LEAD'S INSTRUCTION AND BECAUSE IT WOULD HAVE BEEN A DUPLICATE. The source file's Q4 is a two-part item. Its PRODUCT half - which drawing of the Schedule is the one to work from - is ALREADY Schedule item 4 on this very sheet, and asking it twice inside one workbook would be the drip Rule 55 exists to prevent, in miniature. Its PROCESS half - whether a design may outrank the written description in OUR OWN method - is a decision for the QA LEAD, not for Branko, and has been put to him separately. Branko is asked which drawing is canonical; he is not asked to rule on our sourcing rules.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>THE BUILD WAS NOT OBSERVED (Standing Rules 12, 49, 60). The shared QA sign-in is dead - a read-only probe returned HTTP 401 {"error":"sso_required"} - and quick-login and switch-user were deliberately NOT called, because both rotate the shared session and would sign concurrent workers out of the other branches. BOTH BRANCHES HAVE ALSO REDEPLOYED: sv8785.qa.shopview.com now reads app-version v3.4.2-280ca5a (last-modified Thu 06 Aug 2026 09:37:49 GMT) where the Filters passes ran on v3.4.2-d00239b. So every build-side sentence quoted to Branko - the Status chip behaving as the description says, the filter bar on one row, the capital F - comes from a build that no longer exists, and is worded to him as what the product does rather than as a fresh measurement. All Filters and Schedule verdicts remain PROVISIONAL and the Rule-49 queues are OPEN.</t>
+          <t>WHY ONE FILE AND NOT TWO (Standing Rule 55). build/branko-questions-2026-08-05/ holds a 13-item Branko sheet that is READY TO SEND and WAS NEVER SENT (register row C4). Producing a second sheet without absorbing it would leave the QA lead holding two unsent sheets for the same person - the exact 'drip of separate asks' Rule 55 exists to prevent. So this workbook CARRIES FORWARD all 13 of its items and adds 8 new ones = 21 (4 added when it was first built, and 4 more Schedule items added later the same day from the spec's move to version 25). ⚠️ ACTION NEEDED FROM THE QA LEAD: the 2026-08-05 workbook should be marked SUPERSEDED so an old one cannot go out by mistake. It was NOT edited by this pass, because this task was scoped to write only inside build/filters/questions-2026-08-06/ and build/report-suite/questions-2026-08-06/.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>HOW DRIFT WAS PREVENTED: every carried-forward reader-facing row is IMPORTED from the 2026-08-05 generator's own TAB1/TAB2/TAB3 lists at build time, not retyped. So the 13 carried items are byte-identical to the rows that sheet carried - the same technique the 2026-08-04 Chris consolidation used. Only the 8 new items and the tab notes are new text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>SV-8876 IS DELIBERATELY NOT ON THIS SHEET, AND THE BRIEF FOR THIS TASK WAS WRONG ABOUT IT. The brief listed it as "Ahtasham's clarification question, still his to answer", and CLAUDE.md's Filters section says "Branko owes SV-8876". READ LIVE FROM JIRA 2026-08-06: SV-8876 is a Task, status DONE, resolution Done, resolved 2026-08-05T08:38:16-0500, parent SV-8785, reporter Ahtasham Amjad. He CLOSED IT HIMSELF, with one comment, verbatim: "closing this as it was a gap with test case , I've updated the test case here &gt;&gt;https://shopview.testrail.io/index.php?/cases/view/29557 And created a story defect &gt;&gt; as the build is not behaving as per PRD". Putting it in front of Branko would have re-asked a closed question - the exact embarrassment this project has already had once. THE HALF THAT IS GENUINELY STILL HIS is the narrower one and IS on the sheet, as Filters item 5: did he want the buttons on one row, in which case the developer job should be cancelled? SEPARATE POINT FOR THE QA LEAD, NOT FOR BRANKO: that comment says Ahtasham EDITED OUR CASE C29557. Under Rule 38 we do not touch his cases and he should not be editing ours; this is reported, not acted on.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>THE FILTERS SPEC MOVED TO VERSION 19 THIS MORNING AND NO QUESTION WAS MANUFACTURED FROM IT. Page 572030978, version 19, 2026-08-06T11:48:47Z. Its visible change on the filter bar is S1-R3, verbatim: "Each chip displays a leading type-icon identifying the filter, the filter name, and a chevron icon indicating it opens a dropdown". THAT IS CLEAR ENOUGH TO TEST - a tester can check that each chip carries a leading icon plus a chevron, and which specific icon belongs to which chip comes from the design node the spec links. So NO ROW WAS ADDED for it (Rule 55 says ask what is unclear; it does not say invent an ask). What v19 did NOT do is resolve anything on this sheet: S9-R2 and S9-R3 are unchanged, and the S12-R2 cross-reference is still wrong. ⚠️ OWED: a proper v18 -&gt; v19 diff. This pass checked the points the sheet depends on, not the whole document, and does not claim to have diffed it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>THE SCHEDULE v23 -&gt; v25 DIFF HAS SINCE BEEN DONE, AND THIS ADDENDUM IS ITS OUTPUT - so the warning that stood here ("we have not diffed it") IS NOW OUT OF DATE and is corrected rather than deleted. Page 713031682 is at VERSION 25 (2026-08-06T09:13:51Z, re-confirmed live for this addendum); CLAUDE.md and build/OUTSTANDING-ITEMS-REGISTER.md still name version 23, and NEITHER WAS EDITED (out of scope for this pass - the record correction is owed). The diff lives at build/schedule/spec-v25-2026-08-06/SPEC-DIFF.md: 2 requirements changed, 1 governing-source change that is not a page edit, 3 cases affected. Its four reader-facing questions are Schedule items 5-8 of this sheet. Also re-confirmed by that diff and unchanged in v25: both shop-closure sentences survive, both click-menu wordings survive, and all six engineering-only topics are still absent - so items 1-3 and tab 3 stand exactly as written.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>WORDING RULES APPLIED (Standing Rules 7 and 55): every reader-facing question row names the PROJECT (Filters or Schedule) and the SCREEN, because Branko owns THREE projects - Filters, Schedule and Global Search - so a row read on its own, days later, on a phone must still be unambiguous. Story and epic keys appear in plain form only where they orient him. No case IDs, no requirement anchors, no technical terms and not the word VIU appear anywhere he reads. Each question is a plain A/B/C with a blank for the answer, and each carries a one-line reason so the consequence is visible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>SOURCE-CURRENCY (Standing Rules 31 and 59), fetched LIVE and re-read immediately before writing, 2026-08-06: Filters spec page 572030978 = VERSION 19, HTTP 200 (in-body field still reads "Version: 1.6" - the Rule-31(a) trap; the CONFLUENCE number is the one used). Schedule spec page 713031682 = VERSION 25, HTTP 200, and STALE against our records at 23. Jira read live for SV-8876, SV-8825, SV-8915, SV-8916, SV-8917. TestRail read live for all 114 Filters cases. Designs = PARTIAL, and which artefact is canonical is Schedule item 4 on this very sheet. ADDENDUM, 2026-08-06: for the four new Schedule items the Schedule spec was RE-FETCHED live (page 713031682, version 25, HTTP 200, by Branko Cicovic at 09:13:51Z) and every sentence they rest on was searched in its body; JIRA was read live and read-only for SV-8686, SV-8695, SV-8829, SV-8874, SV-8837 and SV-8915; and FOUR SCHEDULE CASES WERE PULLED LIVE FROM TESTRAIL - C30041, C30012, C30011 and C30001, all HTTP 200, titles, refs and automation markers read from the live cases rather than from our records. So the earlier line saying "Schedule cases were NOT re-pulled this pass" now holds only for the THREE HELD C-ids on items 1-3 (C29983, C30089, C43555), which still come from committed records and are still cited as such.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>THE BUILD WAS NOT OBSERVED (Standing Rules 12, 49, 60). The shared QA sign-in is dead - a read-only probe returned HTTP 401 {"error":"sso_required"} - and quick-login and switch-user were deliberately NOT called, because both rotate the shared session and would sign concurrent workers out of the other branches. BOTH BRANCHES HAVE ALSO REDEPLOYED: sv8785.qa.shopview.com now reads app-version v3.4.2-280ca5a (last-modified Thu 06 Aug 2026 09:37:49 GMT) where the Filters passes ran on v3.4.2-d00239b. So every build-side sentence quoted to Branko - the Status chip behaving as the description says, the filter bar on one row, the capital F - comes from a build that no longer exists, and is worded to him as what the product does rather than as a fresh measurement. All Filters and Schedule verdicts remain PROVISIONAL and the Rule-49 queues are OPEN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>NOTHING HAS BEEN WRITTEN ANYWHERE. This sheet is a draft for the QA lead to send. Read-only on TestRail (get_sections, get_cases), on Confluence (GET content) and on Jira (GET issue). No TestRail write, no Jira write, no case edit, no run write, no application call. CLAUDE.md, build/OUTSTANDING-ITEMS-REGISTER.md and build/APP-ACTIONS-PLAYBOOK.md were not touched, and neither was the 2026-08-05 Branko workbook.</t>
         </is>

--- a/build/filters/questions-2026-08-06/Questions-for-Branko-Cicovic_Filters-and-Schedule_2026-08-06.xlsx
+++ b/build/filters/questions-2026-08-06/Questions-for-Branko-Cicovic_Filters-and-Schedule_2026-08-06.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,6 +34,10 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
     </font>
   </fonts>
   <fills count="4">
@@ -68,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -80,6 +84,9 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -459,73 +466,81 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>*** SUPERSEDED 2026-08-06 — DO NOT SEND THIS FILE. The version to send is Questions-for-Branko-Cicovic_Filters-and-Schedule_Friendly-Version_2026-08-06.xlsx (plain-language twin Questions-for-Branko-Cicovic_Filters-and-Schedule_Friendly-Version_2026-08-06.md) in this same folder: same substance, reordered by what to do first and rewritten to read easily. This file is kept only as the record of what was verified and when.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Filters - questions for Branko Cicovic - 2026-08-06</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>PLEASE START WITH QUESTION 1 - four tests are on hold on it, and it is the one where your own answer and your written description disagree. Question 2 is the biggest single blocker on this project: ten tests are waiting on it. Nothing here is a complaint, and one of these is honestly our own fault for not sending it sooner. It covers TWO of your projects, so every question says which one it belongs to - Filters or Schedule - and the tabs are split the same way. It is gathered into one place so you can go through it in a single sitting rather than getting a trickle of separate messages.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Topic</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>What happens now</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>The question</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Options</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Your answer</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="6" ht="300" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>SEVEN FILTERS ITEMS - FOURTEEN TESTS ARE ON HOLD ACROSS THEM</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="300" customHeight="1">
-      <c r="A6" s="6" t="n">
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="300" customHeight="1">
+      <c r="A7" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Filters (the filter buttons on the Work Orders list) - the Status button on the Estimates and Completed tabs (the story about how filters behave on each tab, SV-8794, under epic SV-8785)</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>PLEASE START HERE ON THIS TAB - four of our tests are on hold on this one point, and two answers are on record that disagree with each other.
 The Work Orders list has tabs across the top. Two of them - Estimates and Completed - already show you only one kind of work order. There is also a row of filter buttons below, and one of them is Status.
@@ -534,30 +549,30 @@
 Why we are asking rather than choosing: we have put the four tests back to your July answer, because that is what you and our QA lead actually decided - but the product currently behaves the way the written description says. So one of the three has to change and it is your call which.</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>Which is right - is the Status button hidden on the Estimates and Completed tabs, or shown greyed out and already filled in?</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>A) NOT SHOWN AT ALL on those two tabs - the written description is right, and my July answer is out of date.
 B) SHOWN, GREYED OUT AND ALREADY FILLED IN - my July answer stands, and the written description needs correcting. (Then we will also raise it so the product can be fixed.)
 C) Something else - please describe it.</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr"/>
-    </row>
-    <row r="7" ht="300" customHeight="1">
-      <c r="A7" s="6" t="n">
+      <c r="F7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8" ht="300" customHeight="1">
+      <c r="A8" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Filters (the filter buttons on the Work Orders list) - the Parts and Reports write-up (under epic SV-8785)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>GENTLE STATUS ASK, not a new question - we know this is already with you and we are not chasing.
 Eight of our tests cover filter buttons on the Parts pages and the Reports pages. They were written from the designs back in July, and they are parked because that part of the product is not built yet and because your write-up for it has not arrived.
@@ -565,90 +580,90 @@
 Why we are asking: only so we can tell our own management honestly whether this is weeks away or months.</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>Roughly when do you expect the Parts and Reports write-up, and is that part of the product still planned for this release?</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>A) It is coming shortly, and it is still in this release.
 B) It has moved to a later release - please say roughly when.
 C) It has been dropped. (Then we will ask about deleting the eight tests.)</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr"/>
-    </row>
-    <row r="8" ht="300" customHeight="1">
-      <c r="A8" s="6" t="n">
+      <c r="F8" s="6" t="inlineStr"/>
+    </row>
+    <row r="9" ht="300" customHeight="1">
+      <c r="A9" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Filters (the filter buttons on the report pages) - the date filter and the page's web address (the story about sharing a filtered view by link, SV-8796, under epic SV-8785)</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>When you pick a date range on a report, the page's web address changes so the view can be shared or bookmarked. Our tests check that the address changes and that a shared link works. They do not check the exact shape of the address, because nothing written down says what that shape should be.
 An engineering note does suggest a shape, but the product appears to do something different, and part of that same note has already been overtaken by your update of 4 August.
 Why we are asking: our automation engineer raised this, and we would rather leave the gap open honestly than invent a rule from an engineering note. No test has been written for it.</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>Is the exact shape of the web address something we should be testing?</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>A) No - it is enough that the link works when it is shared. Do not test the exact shape.
 B) Yes, it matters - and here is the shape it must be: ____________________
 C) Ask engineering to settle it and write it down; treat it as their documentation rather than as a test.</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr"/>
-    </row>
-    <row r="9" ht="300" customHeight="1">
-      <c r="A9" s="6" t="n">
+      <c r="F9" s="6" t="inlineStr"/>
+    </row>
+    <row r="10" ht="300" customHeight="1">
+      <c r="A10" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>Filters (the filter buttons on the Work Orders list, on a phone) - the Imported choice (the mobile filter bar story, SV-8797, under epic SV-8785)</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>Imported sits in the Status list but behaves differently from the others: while it is chosen, the other filters cannot be used. That much is written down, and we have now added a test for it on a phone.
 There is a second behaviour that is not written down anywhere. We are told the product also does the reverse: if you pick an ordinary status last, Imported is quietly un-picked for you.
 Why we are asking rather than just testing it: that behaviour exists only in the developers' own code checks. We do not turn something the code happens to do into something the product must do - that has to be your decision, or it stops being a test of the product and becomes a description of it.</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>Is that reverse behaviour intended - picking an ordinary status last automatically un-picks Imported?</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>A) Yes - that is intended. We will test it, and it should be written down.
 B) No - that is not intended. (Then we will raise it.)
 C) Something else - please describe what should happen.</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr"/>
-    </row>
-    <row r="10" ht="300" customHeight="1">
-      <c r="A10" s="6" t="n">
+      <c r="F10" s="6" t="inlineStr"/>
+    </row>
+    <row r="11" ht="300" customHeight="1">
+      <c r="A11" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Filters (the filter buttons on the Work Orders list) - where the filter bar sits (the filter bar layout story, SV-8786, under epic SV-8785)</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>Your description says the filter bar sits BELOW the row of tabs (All, Estimates, Completed, My Work Orders). The design shows the same thing. In the product the five filter buttons sit ON THE SAME ROW as the tabs.
 One of our own tests used to wave this away with a note saying the product behaves this way "on purpose for now" - and nothing anywhere backed that up. That note was wrong and it has been removed. Our test now expects what your description says.
@@ -656,58 +671,58 @@
 Why we are asking: if you actually wanted them on one row, that developer job should be cancelled and your description updated instead. Better to ask you now than after the change has been made.</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>Should the filter buttons be moved below the tabs, or did you want them on the same row as the tabs?</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>A) MOVE THEM BELOW - as your description and the design say. The developer job is correct and nothing needs changing in writing.
 B) SAME ROW IS WHAT I WANTED - then the developer job should be cancelled and the description updated to say so.</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr"/>
-    </row>
-    <row r="11" ht="300" customHeight="1">
-      <c r="A11" s="6" t="n">
+      <c r="F11" s="6" t="inlineStr"/>
+    </row>
+    <row r="12" ht="300" customHeight="1">
+      <c r="A12" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Filters (the filter buttons on the Work Orders list) - the wording on the phone button (the mobile filter bar story, SV-8797, under epic SV-8785)</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>This is a tiny one, and it exists only because our tests have to quote the exact words a tester will see on screen.
 Your description calls the button "Apply filters", with a small f. On a phone the button actually reads "Apply Filters", with a capital F.
 Why we are asking: we would rather your description and the screen said the same thing than have our test quietly differ from one of them.</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>Which spelling is the right one?</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>A) "Apply Filters" with a capital F - the description can be tidied to match the screen.
 B) "Apply filters" with a small f - then the button on screen should be corrected.</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr"/>
-    </row>
-    <row r="12" ht="300" customHeight="1">
-      <c r="A12" s="6" t="n">
+      <c r="F12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>Filters (the filter buttons on the Work Orders list) - a pointer in your own description that leads to the wrong place (the mobile filter bar story, SV-8797, under epic SV-8785)</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>NO DECISION NEEDED - this is just a helpful heads-up about a typo-level slip, and it has already cost one round of confusion.
 In the phone section, the paragraph about the filter buttons says they work like the desktop "with one exception", and then points the reader at a numbered paragraph further down. But the paragraph it points at is the one about the page search box - not an exception at all. The real exception, that a phone only filters when the person taps the apply button, is the very next paragraph after the one it points to.
@@ -715,17 +730,17 @@
 Why we are telling you: a reader who follows that pointer lands on the wrong paragraph and concludes there is no exception.</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>Nothing to decide - please just repoint that reference to the apply-button paragraph next time you have the document open.</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>(No options - noted for your next edit.)</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr"/>
+      <c r="F13" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
